--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N96_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N96_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.62659809585964</v>
+        <v>9.851822190577192</v>
       </c>
       <c r="D2" t="n">
-        <v>60.80778560084786</v>
+        <v>9.881265160137778</v>
       </c>
       <c r="E2" t="n">
-        <v>16.97790637804032</v>
+        <v>2.758909786431551</v>
       </c>
       <c r="F2" t="n">
-        <v>17.08552343619706</v>
+        <v>2.776397558382024</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.48986454932512</v>
+        <v>10.96710298926533</v>
       </c>
       <c r="D3" t="n">
-        <v>67.68175734925822</v>
+        <v>10.99828556925446</v>
       </c>
       <c r="E3" t="n">
-        <v>16.97790637804032</v>
+        <v>2.758909786431551</v>
       </c>
       <c r="F3" t="n">
-        <v>17.08552343619706</v>
+        <v>2.776397558382024</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.47681253368697</v>
+        <v>4.302482036724133</v>
       </c>
       <c r="D4" t="n">
-        <v>26.54062926046106</v>
+        <v>4.312852254824923</v>
       </c>
       <c r="E4" t="n">
-        <v>16.97790637804032</v>
+        <v>2.758909786431551</v>
       </c>
       <c r="F4" t="n">
-        <v>17.08552343619706</v>
+        <v>2.776397558382024</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.23281191866253</v>
+        <v>4.912831936782662</v>
       </c>
       <c r="D5" t="n">
-        <v>30.1725283718038</v>
+        <v>4.903035860418117</v>
       </c>
       <c r="E5" t="n">
-        <v>16.97790637804032</v>
+        <v>2.758909786431551</v>
       </c>
       <c r="F5" t="n">
-        <v>17.08552343619706</v>
+        <v>2.776397558382024</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.18250788122229</v>
+        <v>5.717157530698621</v>
       </c>
       <c r="D6" t="n">
-        <v>35.06795916510148</v>
+        <v>5.69854336432899</v>
       </c>
       <c r="E6" t="n">
-        <v>16.97790637804032</v>
+        <v>2.758909786431551</v>
       </c>
       <c r="F6" t="n">
-        <v>17.08552343619706</v>
+        <v>2.776397558382024</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.24381654225876</v>
+        <v>4.752120188117048</v>
       </c>
       <c r="D7" t="n">
-        <v>29.07481393569903</v>
+        <v>4.724657264551093</v>
       </c>
       <c r="E7" t="n">
-        <v>16.97790637804032</v>
+        <v>2.758909786431551</v>
       </c>
       <c r="F7" t="n">
-        <v>17.08552343619706</v>
+        <v>2.776397558382024</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.04837103813739</v>
+        <v>3.095360293697325</v>
       </c>
       <c r="D8" t="n">
-        <v>18.97034369735564</v>
+        <v>3.082680850820292</v>
       </c>
       <c r="E8" t="n">
-        <v>16.97790637804032</v>
+        <v>2.758909786431551</v>
       </c>
       <c r="F8" t="n">
-        <v>17.08552343619706</v>
+        <v>2.776397558382024</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
